--- a/data/BASES/REGISTROC.xlsx
+++ b/data/BASES/REGISTROC.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="63">
   <si>
     <t>FECHA</t>
   </si>
@@ -196,6 +196,24 @@
   </si>
   <si>
     <t>$ 5,776.30</t>
+  </si>
+  <si>
+    <t>sabri02</t>
+  </si>
+  <si>
+    <t>$ 118.60</t>
+  </si>
+  <si>
+    <t>$ 18.98</t>
+  </si>
+  <si>
+    <t>$ 137.58</t>
+  </si>
+  <si>
+    <t>OBSERVACIONES</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -241,9 +259,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
@@ -593,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D375DD-15B7-4F53-9122-30FA48C9EA3E}">
-  <dimension ref="A1:AA9"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="9.44140625" collapsed="true"/>
@@ -701,6 +725,9 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
@@ -1036,6 +1063,163 @@
         <v>36</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B10" t="n" s="17">
+        <v>46322.0</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" t="n" s="18">
+        <v>46331.52098165509</v>
+      </c>
+      <c r="M10" t="n" s="19">
+        <v>46348.521260636575</v>
+      </c>
+      <c r="N10" t="s">
+        <v>35</v>
+      </c>
+      <c r="O10" t="s">
+        <v>36</v>
+      </c>
+      <c r="P10" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R10" t="s">
+        <v>38</v>
+      </c>
+      <c r="S10" t="s">
+        <v>39</v>
+      </c>
+      <c r="T10" t="s">
+        <v>58</v>
+      </c>
+      <c r="U10" t="s">
+        <v>59</v>
+      </c>
+      <c r="V10" t="s">
+        <v>60</v>
+      </c>
+      <c r="W10" t="s">
+        <v>35</v>
+      </c>
+      <c r="X10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B11" t="n" s="20">
+        <v>46322.0</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" t="n" s="21">
+        <v>46326.55569712963</v>
+      </c>
+      <c r="M11" t="n" s="22">
+        <v>46326.555729085645</v>
+      </c>
+      <c r="N11" t="s">
+        <v>35</v>
+      </c>
+      <c r="O11" t="s">
+        <v>36</v>
+      </c>
+      <c r="P11" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>30</v>
+      </c>
+      <c r="R11" t="s">
+        <v>38</v>
+      </c>
+      <c r="S11" t="s">
+        <v>39</v>
+      </c>
+      <c r="T11" t="s">
+        <v>58</v>
+      </c>
+      <c r="U11" t="s">
+        <v>59</v>
+      </c>
+      <c r="V11" t="s">
+        <v>60</v>
+      </c>
+      <c r="W11" t="s">
+        <v>35</v>
+      </c>
+      <c r="X11" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
